--- a/backend/samples/financial_model_v2.xlsx
+++ b/backend/samples/financial_model_v2.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Assumptions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Revenue" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Costs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Income Statement" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Costs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -93,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -105,6 +107,8 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -476,7 +480,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Key Financial Assumptions</t>
+          <t>Key Financial Assumptions (FY 2024 Actual)</t>
         </is>
       </c>
     </row>
@@ -983,20 +987,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Executive Income Statement</t>
+          <t>Executive Income Statement (Laporan Laba Rugi)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Metric / Account</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1109,7 +1113,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Income Tax (22%)</t>
+          <t>Income Tax</t>
         </is>
       </c>
       <c r="B7" s="5">
@@ -1158,6 +1162,884 @@
       <c r="F8" s="10">
         <f>F6-F7</f>
         <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI Cloud Infrastructure Fee</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>28000</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>83000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Executive Balance Sheet (Neraca)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Balance Sheet Account</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Year End</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cash &amp; Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>145000</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>142000</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>168000</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>195000</v>
+      </c>
+      <c r="F4" s="5">
+        <f>E4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B5" s="5">
+        <f>Revenue!D8*0.14</f>
+        <v/>
+      </c>
+      <c r="C5" s="5">
+        <f>Revenue!E8*0.14</f>
+        <v/>
+      </c>
+      <c r="D5" s="5">
+        <f>Revenue!F8*0.14</f>
+        <v/>
+      </c>
+      <c r="E5" s="5">
+        <f>Revenue!G8*0.14</f>
+        <v/>
+      </c>
+      <c r="F5" s="5">
+        <f>E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Inventories</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>85000</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>88000</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>92000</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>95000</v>
+      </c>
+      <c r="F6" s="5">
+        <f>E6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Total Current Assets</t>
+        </is>
+      </c>
+      <c r="B7" s="8">
+        <f>SUM(B4:B6)</f>
+        <v/>
+      </c>
+      <c r="C7" s="8">
+        <f>SUM(C4:C6)</f>
+        <v/>
+      </c>
+      <c r="D7" s="8">
+        <f>SUM(D4:D6)</f>
+        <v/>
+      </c>
+      <c r="E7" s="8">
+        <f>SUM(E4:E6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="8">
+        <f>E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Property, Plant &amp; Equipment (Net)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>490000</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>440000</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>430000</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>420000</v>
+      </c>
+      <c r="F8" s="5">
+        <f>E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>58000</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F9" s="5">
+        <f>E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="12">
+        <f>B7+B8+B9</f>
+        <v/>
+      </c>
+      <c r="C10" s="12">
+        <f>C7+C8+C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="12">
+        <f>D7+D8+D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="12">
+        <f>E7+E8+E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="12">
+        <f>E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B11" s="5">
+        <f>Costs!C8*0.12</f>
+        <v/>
+      </c>
+      <c r="C11" s="5">
+        <f>Costs!D8*0.12</f>
+        <v/>
+      </c>
+      <c r="D11" s="5">
+        <f>Costs!E8*0.12</f>
+        <v/>
+      </c>
+      <c r="E11" s="5">
+        <f>Costs!F8*0.12</f>
+        <v/>
+      </c>
+      <c r="F11" s="5">
+        <f>E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Short-Term Debt</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F12" s="5">
+        <f>E12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Total Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B13" s="8">
+        <f>SUM(B11:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="8">
+        <f>SUM(C11:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="8">
+        <f>SUM(D11:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="8">
+        <f>SUM(E11:E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="8">
+        <f>E13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Long-Term Debt</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>220000</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>190000</v>
+      </c>
+      <c r="F14" s="5">
+        <f>E14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="B15" s="8">
+        <f>B13+B14</f>
+        <v/>
+      </c>
+      <c r="C15" s="8">
+        <f>C13+C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="8">
+        <f>D13+D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="8">
+        <f>E13+E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="8">
+        <f>E15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F16" s="5">
+        <f>E16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="5">
+        <f>B10-B15-B16</f>
+        <v/>
+      </c>
+      <c r="C17" s="5">
+        <f>C10-C15-C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="5">
+        <f>D10-D15-D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="5">
+        <f>E10-E15-E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="5">
+        <f>E17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Total Shareholders' Equity</t>
+        </is>
+      </c>
+      <c r="B18" s="8">
+        <f>B16+B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="8">
+        <f>C16+C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="8">
+        <f>D16+D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="8">
+        <f>E16+E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="8">
+        <f>E18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Total Liabilities &amp; Equity</t>
+        </is>
+      </c>
+      <c r="B19" s="12">
+        <f>B15+B18</f>
+        <v/>
+      </c>
+      <c r="C19" s="12">
+        <f>C15+C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="12">
+        <f>D15+D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="12">
+        <f>E15+E18</f>
+        <v/>
+      </c>
+      <c r="F19" s="12">
+        <f>E19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Digital &amp; Crypto Assets</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>22000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Executive Cash Flow Statement (Laporan Arus Kas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Cash Flow Account</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Full Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="B4" s="5">
+        <f>'Income Statement'!B8</f>
+        <v/>
+      </c>
+      <c r="C4" s="5">
+        <f>'Income Statement'!C8</f>
+        <v/>
+      </c>
+      <c r="D4" s="5">
+        <f>'Income Statement'!D8</f>
+        <v/>
+      </c>
+      <c r="E4" s="5">
+        <f>'Income Statement'!E8</f>
+        <v/>
+      </c>
+      <c r="F4" s="5">
+        <f>'Income Statement'!F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortization</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F5" s="5">
+        <f>SUM(B5:E5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Change in Working Capital</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>-6000</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F6" s="5">
+        <f>SUM(B6:E6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Net Cash from Operating Activities</t>
+        </is>
+      </c>
+      <c r="B7" s="12">
+        <f>SUM(B4:B6)</f>
+        <v/>
+      </c>
+      <c r="C7" s="12">
+        <f>SUM(C4:C6)</f>
+        <v/>
+      </c>
+      <c r="D7" s="12">
+        <f>SUM(D4:D6)</f>
+        <v/>
+      </c>
+      <c r="E7" s="12">
+        <f>SUM(E4:E6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="12">
+        <f>SUM(F4:F6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Capital Expenditures (CapEx)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>-32000</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-25000</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-18000</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-12000</v>
+      </c>
+      <c r="F8" s="5">
+        <f>SUM(B8:E8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Net Cash from Investing Activities</t>
+        </is>
+      </c>
+      <c r="B9" s="8">
+        <f>B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="8">
+        <f>C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="8">
+        <f>D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="8">
+        <f>E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="8">
+        <f>SUM(B9:E9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Repayment of Debt</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="F10" s="5">
+        <f>SUM(B10:E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Dividends Paid</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-12000</v>
+      </c>
+      <c r="F11" s="5">
+        <f>SUM(B11:E11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Net Cash from Financing Activities</t>
+        </is>
+      </c>
+      <c r="B12" s="8">
+        <f>SUM(B10:B11)</f>
+        <v/>
+      </c>
+      <c r="C12" s="8">
+        <f>SUM(C10:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="8">
+        <f>SUM(D10:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="8">
+        <f>SUM(E10:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="8">
+        <f>SUM(F10:F11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Net Increase / Decrease in Cash</t>
+        </is>
+      </c>
+      <c r="B13" s="12">
+        <f>B7+B9+B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="12">
+        <f>C7+C9+C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="12">
+        <f>D7+D9+D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="12">
+        <f>E7+E9+E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="12">
+        <f>SUM(B13:E13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Beginning Cash Balance</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C14" s="5">
+        <f>B15</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>C15</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>D15</f>
+        <v/>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Ending Cash Balance</t>
+        </is>
+      </c>
+      <c r="B15" s="12">
+        <f>B13+B14</f>
+        <v/>
+      </c>
+      <c r="C15" s="12">
+        <f>C13+C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="12">
+        <f>D13+D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="12">
+        <f>E13+E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="12">
+        <f>E15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share Buyback Program</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-45000</v>
       </c>
     </row>
   </sheetData>
